--- a/backend/verification_results.xlsx
+++ b/backend/verification_results.xlsx
@@ -45,14 +45,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00fff1f2"/>
-        <bgColor rgb="00fff1f2"/>
+        <fgColor rgb="00f0fdf4"/>
+        <bgColor rgb="00f0fdf4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00f0fdf4"/>
-        <bgColor rgb="00f0fdf4"/>
+        <fgColor rgb="00fff1f2"/>
+        <bgColor rgb="00fff1f2"/>
       </patternFill>
     </fill>
   </fills>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -484,700 +484,700 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Certificate-4.pdf (1) - Copy.pdf</t>
+          <t>08 Pranav.C.pdf</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Chaitanya Sonawane</t>
+          <t>Pranav Choudhary</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>ReactJS</t>
+          <t>Cyber Security and Applied Ethical Hacking</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>July 11, 2025</t>
+          <t>2026-04-28T18:55:39Z</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Fraud</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Certificate-4.pdf (1).pdf</t>
+          <t>09.Rushikesh Daware.pdf</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Chaitanya Sonawane</t>
+          <t>Rushikesh Daware</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>ReactJS</t>
+          <t>Cyber Security and Applied Ethical Hacking</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>July 11, 2025</t>
+          <t>2026-04-26T12:52:57Z</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Fraud</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Certificate-4.pdf (2) - Copy.pdf</t>
+          <t>10 Cyber Security - Ganesh Deshmukh.pdf</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Chaitanya Sonawane</t>
+          <t>Ganesh Deshmukh</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>ReactJS</t>
+          <t>Cyber Security and Applied Ethical Hacking</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>July 11, 2025</t>
+          <t>2026-05-01T15:28:22Z</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Fraud</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Certificate-4.pdf (3) - Copy.pdf</t>
+          <t>18 Chetana Hyalij.pdf</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Chaitanya Sonawane</t>
+          <t>Chetana Hyalij</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>ReactJS</t>
+          <t>Cyber Security and Applied Ethical Hacking</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>July 11, 2025</t>
+          <t>2026-04-28T14:57:10Z</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Fraud</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Certificate-4.pdf (4) - Copy.pdf</t>
+          <t>21.Snehal Jadhav.pdf</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Chaitanya Sonawane</t>
+          <t>Snehal Jadhav</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>ReactJS</t>
+          <t>Cyber Security and Applied Ethical Hacking</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>July 11, 2025</t>
+          <t>2026-04-25T12:49:10Z</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Fraud</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Certificate-4.pdf (5) - Copy.pdf</t>
+          <t>26 Paras Kulkarni.pdf</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Chaitanya Sonawane</t>
+          <t>Paras Kulkarni</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>ReactJS</t>
+          <t>Cyber Security and Applied Ethical Hacking</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>July 11, 2025</t>
+          <t>2026-01-07T12:39:02Z</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Fraud</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Certificate-4.pdf (6) - Copy.pdf</t>
+          <t>34 Kalpesh.pdf</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Chaitanya Sonawane</t>
+          <t>Kalpesh Musale</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>ReactJS</t>
+          <t>Cyber Security and Applied Ethical Hacking</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>July 11, 2025</t>
+          <t>2026-04-25T17:09:09Z</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Fraud</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Certificate-4.pdf (7) - Copy.pdf</t>
+          <t>35 Saee Nerkar (3).pdf</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Chaitanya Sonawane</t>
+          <t>Saee Nerkar</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>ReactJS</t>
+          <t>Cyber Security and Applied Ethical Hacking</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>July 11, 2025</t>
+          <t>2026-02-20T16:35:27Z</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Fraud</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Certificate-4.pdf (8) - Copy.pdf</t>
+          <t>38_Abhishek Cyber Security.pdf</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Chaitanya Sonawane</t>
+          <t>Abhishek Patil</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>ReactJS</t>
+          <t>Cyber Security and Applied Ethical Hacking</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>July 11, 2025</t>
+          <t>2026-04-26T10:14:23Z</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Fraud</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Certificate-4.pdf (9) - Copy.pdf</t>
+          <t>42 Jayesh Pawar.pdf</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Chaitanya Sonawane</t>
+          <t>JAYESH PAWAR</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>ReactJS</t>
+          <t>Cyber Security and Applied Ethical Hacking</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>July 11, 2025</t>
+          <t>2026-04-25T08:11:41Z</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Fraud</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Certificate-4.pdf (10) - Copy.pdf</t>
+          <t>43- SWAMI PAWAR.pdf</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Chaitanya Sonawane</t>
+          <t>Swami Pawar</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>ReactJS</t>
+          <t>Cyber Security and Applied Ethical Hacking</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>July 11, 2025</t>
+          <t>2026-04-13T04:51:20Z</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Fraud</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Certificate-4.pdf (11) - Copy.pdf</t>
+          <t>45 Pushkar Gaikwad.pdf</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Chaitanya Sonawane</t>
+          <t>Pushkar Gaikwad</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>ReactJS</t>
+          <t>Cyber Security and Applied Ethical Hacking</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>July 11, 2025</t>
+          <t>2026-04-26T18:54:30Z</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Fraud</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Certificate-4.pdf (12) - Copy.pdf</t>
+          <t>57_Aarya Shinde.pdf</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Chaitanya Sonawane</t>
+          <t>Aarya Shinde</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>ReactJS</t>
+          <t>Cyber Security and Applied Ethical Hacking</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>July 11, 2025</t>
+          <t>2026-01-10T09:59:58Z</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Fraud</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Certificate-4.pdf (13) - Copy.pdf</t>
+          <t>59 Kshiti Shirsath CS.pdf</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Chaitanya Sonawane</t>
+          <t>Kshiti Shirsath</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>ReactJS</t>
+          <t>Cyber Security and Applied Ethical Hacking</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>July 11, 2025</t>
+          <t>2026-02-10T09:35:53Z</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Fraud</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Certificate-4.pdf (14) - Copy.pdf</t>
+          <t>64_Tanmay Sonawane.pdf</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Chaitanya Sonawane</t>
+          <t>Tanmay Sonawane</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>ReactJS</t>
+          <t>Cyber Security and Applied Ethical Hacking</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>July 11, 2025</t>
+          <t>2026-04-11T08:16:39Z</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Fraud</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Certificate-4.pdf (15) - Copy.pdf</t>
+          <t>68.DigvijayThakre.pdf</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
+          <t>Digvijay Thakre</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Cyber Security and Applied Ethical Hacking</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-03T05:07:48Z</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>73_Riya Wadhe.pdf</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Riya Wadhe</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Project on Deep Learning - Artificial Neural Network</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13T16:24:26Z</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>76_Yugandhara Patil .pdf</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Yugandhara Patil</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Cyber Security and Applied Ethical Hacking</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-12T08:40:51Z</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Aditya_Yadav_75.pdf</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Aditya Yadav</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Cyber Security and Applied Ethical Hacking</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-26T12:11:39Z</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Anushri Amritkar.pdf</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Anushri Amritkar</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Cyber Security and Applied Ethical Hacking</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-12T10:52:13Z</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Arti 52.pdf</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>arti sangle</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Cyber Security and Applied Ethical Hacking</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-23T19:19:48Z</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Chaitanya Sonawane (61)- CS.pdf</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>Chaitanya Sonawane</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>ReactJS</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>July 11, 2025</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Fraud</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>Samiksha Rote_50 - Copy (2).pdf</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Samiksha Rote</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>Project on Deep Learning - Artificial Neural Network</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>February 8,2026</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>Samiksha Rote_50 - Copy (3).pdf</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Samiksha Rote</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Project on Deep Learning - Artificial Neural Network</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>February 8,2026</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>Samiksha Rote_50 - Copy (4).pdf</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>Samiksha Rote</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>Project on Deep Learning - Artificial Neural Network</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>February 8,2026</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>Samiksha Rote_50 - Copy (5).pdf</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Samiksha Rote</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>Project on Deep Learning - Artificial Neural Network</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>February 8,2026</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>Samiksha Rote_50 - Copy (6).pdf</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Samiksha Rote</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>Project on Deep Learning - Artificial Neural Network</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>February 8,2026</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>Samiksha Rote_50 - Copy (7).pdf</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>Samiksha Rote</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>Project on Deep Learning - Artificial Neural Network</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>February 8,2026</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Cyber Security and Applied Ethical Hacking</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-27T16:01:12Z</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>Samiksha Rote_50 - Copy (8).pdf</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Samiksha Rote</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>Project on Deep Learning - Artificial Neural Network</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>February 8,2026</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>cyber_nimish.pdf</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Nimish Sinkar</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Cyber Security and Applied Ethical Hacking</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28T13:34:21Z</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>Samiksha Rote_50 - Copy (9).pdf</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>Samiksha Rote</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>Project on Deep Learning - Artificial Neural Network</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>February 8,2026</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>damini_shilavat_56.pdf</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Damini Shilavat</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Cyber Security and Applied Ethical Hacking</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-04T14:18:18Z</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>Samiksha Rote_50 - Copy (10).pdf</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>Samiksha Rote</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>Project on Deep Learning - Artificial Neural Network</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>February 8,2026</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Gayatri katkar25.pdf</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Gayatri Katkar</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Cyber Security and Applied Ethical Hacking</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-18T17:01:13Z</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>Samiksha Rote_50 - Copy (11).pdf</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>Samiksha Rote</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>Project on Deep Learning - Artificial Neural Network</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>February 8,2026</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Harshal Satpute CS.pdf</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Harshal Satpute</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Cyber Security and Applied Ethical Hacking</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-23T16:22:53Z</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -1186,322 +1186,607 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Samiksha Rote_50 - Copy (12).pdf</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
+          <t>Himanshu(1).pdf</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n"/>
+      <c r="C28" s="3" t="n"/>
+      <c r="D28" s="3" t="n"/>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>QR Error</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>himanshu.pdf</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Himanshu Bendale</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Cyber Security and Applied Ethical Hacking</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-29T19:03:55Z</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Komal Godse (16).pdf</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Komal Gorakh Godse</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Cyber Security and Applied Ethical Hacking</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-19T15:45:50Z</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Kunal  Magar 29.pdf</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Kunal Magar</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Cyber Security and Applied Ethical Hacking</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-25T11:39:22Z</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Madhulika Gangurde_13.pdf</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Madhulika Gangurde</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Cyber Security and Applied Ethical Hacking</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-07T12:11:01Z</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Mayuri 65.pdf</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Mayuri Surse</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Cyber Security and Applied Ethical Hacking</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-26T19:40:38Z</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Namrata Chavan (07).pdf</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Namrata Chavan</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Cyber Security and Applied Ethical Hacking</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-08T16:06:36Z</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Prayag_.pdf</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Prayag Rajput</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Cyber Security and Applied Ethical Hacking</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-24T10:12:31Z</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Prerana Rajgire (46).pdf</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Prerana Rajgire</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Cyber Security and Applied Ethical Hacking</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-26T10:48:45Z</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Purva_Ugale_71.pdf</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Purva Prashant Ugale</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Cyber Security and Applied Ethical Hacking</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-27T16:54:07Z</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Renuka Gosavi cyber.pdf</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Renuka Gosavi</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Cyber Security and Applied Ethical Hacking</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01T15:02:28Z</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Rohit Jadhav 19.pdf</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Rohit Jadhav</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Cyber Security and Applied Ethical Hacking</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03T04:23:17Z</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Rutika_Rayate_49.pdf</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Rutika Rayate</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Cyber Security and Applied Ethical Hacking</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-11T05:13:38Z</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Sachin_Tekale.67.pdf</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Sachin Tekale</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Cyber Security and Applied Ethical Hacking</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-11T12:17:07Z</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Samiksha Rote_50.pdf</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>Samiksha Rote</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>Project on Deep Learning - Artificial Neural Network</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>February 8,2026</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>Samiksha Rote_50 - Copy (13).pdf</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>Samiksha Rote</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>Project on Deep Learning - Artificial Neural Network</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>February 8,2026</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>Samiksha Rote_50 - Copy (14).pdf</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>Samiksha Rote</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>Project on Deep Learning - Artificial Neural Network</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>February 8,2026</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>Samiksha Rote_50 - Copy.pdf</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>Samiksha Rote</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>Project on Deep Learning - Artificial Neural Network</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>February 8,2026</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>Samiksha Rote_50.pdf</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>Samiksha Rote</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>Project on Deep Learning - Artificial Neural Network</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>February 8,2026</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>Vidhi Gangurde (14) - Copy.pdf</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Cyber Security and Applied Ethical Hacking</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-10T09:37:22Z</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>shreya sathe(53).pdf</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Shreya Sathe</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Cyber Security and Applied Ethical Hacking</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-30T05:27:18Z</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Taiba Shaikh.pdf</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Taiba Shaikh</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Cyber Security and Applied Ethical Hacking</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-18T11:25:29Z</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>UpasanaWagh.pdf</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>UPASANA Wagh</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Cyber Security and Applied Ethical Hacking</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-16T16:00:57Z</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Vaishnavi_Bhandare.pdf</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Vaishnavi Bhandare</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Cyber Security and Applied Ethical Hacking</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-21T14:14:03Z</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Vaishnavi_Dharam.pdf</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Vaishnavi Dharam</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Cyber Security and Applied Ethical Hacking</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-21T13:55:44Z</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Vidhi Gangurde (14).pdf</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>VIDHI GANGURDE</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>Project on Deep Learning - Artificial Neural Network</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>February 4, 2026</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>Vidhi Gangurde (14).pdf</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>VIDHI GANGURDE</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>Project on Deep Learning - Artificial Neural Network</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>February 4, 2026</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>Vidhi Gangurde (15) - Copy.pdf</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>VIDHI GANGURDE</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>Project on Deep Learning - Artificial Neural Network</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>February 4, 2026</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>Vidhi Gangurde (16) - Copy.pdf</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>VIDHI GANGURDE</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>Project on Deep Learning - Artificial Neural Network</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>February 4, 2026</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>Vidhi Gangurde (17) - Copy.pdf</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>VIDHI GANGURDE</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>Project on Deep Learning - Artificial Neural Network</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>February 4, 2026</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>Vidhi Gangurde (18) - Copy.pdf</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>VIDHI GANGURDE</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>Project on Deep Learning - Artificial Neural Network</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>February 4, 2026</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>Vidhi Gangurde (19) - Copy.pdf</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>VIDHI GANGURDE</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>Project on Deep Learning - Artificial Neural Network</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>February 4, 2026</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Cyber Security and Applied Ethical Hacking</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-04T15:27:07Z</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Yash thete.pdf</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Yash Thete</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Cyber Security and Applied Ethical Hacking</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-25T05:51:05Z</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Yash Zoman.pdf</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Yash Zoman</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Cyber Security and Applied Ethical Hacking</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-17T16:09:15Z</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
